--- a/estatemaster-agent/tests/fixtures/models/r32_hold_usd.xlsx
+++ b/estatemaster-agent/tests/fixtures/models/r32_hold_usd.xlsx
@@ -22,7 +22,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t xml:space="preserve">OAKWOOD RETAIL PARK (USD)</t>
+  </si>
   <si>
     <t xml:space="preserve">Year 1 rent</t>
   </si>
@@ -404,11 +407,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77720476"/>
-        <c:axId val="93187557"/>
+        <c:axId val="26367618"/>
+        <c:axId val="60116037"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77720476"/>
+        <c:axId val="26367618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -440,7 +443,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93187557"/>
+        <c:crossAx val="60116037"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -448,7 +451,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93187557"/>
+        <c:axId val="60116037"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -490,7 +493,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77720476"/>
+        <c:crossAx val="26367618"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -757,12 +760,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:B8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1000000</v>
@@ -770,7 +778,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>0.03</v>
@@ -778,7 +786,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0.3</v>
@@ -786,7 +794,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>12000000</v>
@@ -794,7 +802,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>0.065</v>
@@ -802,7 +810,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>10</v>
@@ -810,7 +818,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>0.08</v>
@@ -837,12 +845,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>0</v>
@@ -888,12 +896,12 @@
         <v>10</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>2025</v>
@@ -931,7 +939,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="0" t="n">
         <f aca="false">IF(AND(D$4&gt;=1,D$4&lt;=Inputs!$B$7),Inputs!$B$2*(1+Inputs!$B$3)^(D$4-1),0)</f>
@@ -980,7 +988,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">-D7*Inputs!$B$4</f>
@@ -1029,7 +1037,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="0" t="n">
         <f aca="false">D7+D8</f>
@@ -1078,7 +1086,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>-100000</v>
@@ -1117,7 +1125,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">IF(D$4=Inputs!$B$7,D9*(1+Inputs!$B$3)/Inputs!$B$6,0)</f>
@@ -1166,7 +1174,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">-Inputs!B5</f>
@@ -1179,7 +1187,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">SUM(C9:C12)</f>
@@ -1251,7 +1259,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IRR('Cash Flow'!C13:M13)</f>
@@ -1260,7 +1268,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="n">
         <f aca="false">NPV(Inputs!B8,'Cash Flow'!D13:M13)+'Cash Flow'!C13</f>
@@ -1269,7 +1277,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">SUMIF('Cash Flow'!C13:M13,"&gt;0")/-SUMIF('Cash Flow'!C13:M13,"&lt;0")</f>
@@ -1278,7 +1286,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">'Cash Flow'!M11</f>
@@ -1287,7 +1295,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">'Cash Flow'!N9</f>
@@ -1296,7 +1304,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">'Cash Flow'!N13</f>
